--- a/rezKlasifikacije/rezultati_PCA.xlsx
+++ b/rezKlasifikacije/rezultati_PCA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,161 +468,161 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Stablo odlucivanja + PCA</t>
+          <t>Stablo odlucivanja</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.767639902676399</v>
+        <v>0.768</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2480211081794195</v>
+        <v>0.256</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2460732984293194</v>
+        <v>0.262</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2470433639947437</v>
+        <v>0.769</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8626228722128986</v>
+        <v>0.862</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2470433639947437</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Random Forest + PCA</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.82441200324412</v>
+        <v>0.822</v>
       </c>
       <c r="C3" t="n">
-        <v>0.316546762589928</v>
+        <v>0.295</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1151832460732984</v>
+        <v>0.107</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1689059500959693</v>
+        <v>0.785</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9018363182951712</v>
+        <v>0.9</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1689059500959693</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MLP + PCA</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8438767234387672</v>
+        <v>0.845</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3846153846153846</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01308900523560209</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02531645569620253</v>
+        <v>0.774</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9151421644258321</v>
+        <v>0.916</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02531645569620253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NB + PCA</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8272506082725061</v>
+        <v>0.827</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2843137254901961</v>
+        <v>0.284</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07591623036649214</v>
+        <v>0.076</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1198347107438017</v>
+        <v>0.783</v>
       </c>
       <c r="F5" t="n">
-        <v>0.904226618705036</v>
+        <v>0.904</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1198347107438017</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KNN + PCA</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8021086780210868</v>
+        <v>0.802</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2590909090909091</v>
+        <v>0.259</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1492146596858639</v>
+        <v>0.149</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1893687707641196</v>
+        <v>0.779</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8872979214780601</v>
+        <v>0.887</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1893687707641196</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>lr + PCA</t>
+          <t>LR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8446877534468775</v>
+        <v>0.845</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.444</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01047120418848168</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02046035805626599</v>
+        <v>0.777</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9156573441973134</v>
+        <v>0.916</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02046035805626599</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SVM + PCA</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8450932684509327</v>
+        <v>0.845</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -631,10 +631,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.774</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9160439560439561</v>
+        <v>0.916</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -643,26 +643,51 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XGB + PCA</t>
+          <t>XGB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8292781832927818</v>
+        <v>0.829</v>
       </c>
       <c r="C9" t="n">
-        <v>0.208955223880597</v>
+        <v>0.209</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03664921465968586</v>
+        <v>0.037</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0623608017817372</v>
+        <v>0.775</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9060896720945795</v>
+        <v>0.906</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0623608017817372</v>
+        <v>0.062</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NN</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
